--- a/sales_data.xlsx
+++ b/sales_data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="71">
   <si>
     <t>訂單日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -122,55 +122,164 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>電腦周邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電腦周邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>音訊設備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手機配件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手機配件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電腦周邊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>音訊設備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辦公用品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>儲存設備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>總銷售額</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平均銷售額</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>單日銷售額</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2月訂單資料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ORD011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ORD012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ORD013</t>
+  </si>
+  <si>
+    <t>ORD014</t>
+  </si>
+  <si>
+    <t>ORD015</t>
+  </si>
+  <si>
+    <t>ORD016</t>
+  </si>
+  <si>
+    <t>ORD017</t>
+  </si>
+  <si>
+    <t>ORD018</t>
+  </si>
+  <si>
+    <t>ORD019</t>
+  </si>
+  <si>
+    <t>ORD020</t>
+  </si>
+  <si>
+    <t>無線滑鼠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藍芽耳機</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>音訊設備</t>
+  </si>
+  <si>
+    <t>音訊設備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行動電源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手機配件</t>
+  </si>
+  <si>
+    <t>手機配件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>電腦周邊</t>
+  </si>
+  <si>
+    <t>辦公用品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>儲存設備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1月訂單資料</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>電腦周邊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>電腦周邊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>音訊設備</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>手機配件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>手機配件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>電腦周邊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>音訊設備</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>辦公用品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>儲存設備</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>總銷售額</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>平均銷售額</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>單日銷售額</t>
+    <t>ORD021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ORD022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ORD023</t>
+  </si>
+  <si>
+    <t>ORD024</t>
+  </si>
+  <si>
+    <t>ORD025</t>
+  </si>
+  <si>
+    <t>ORD026</t>
+  </si>
+  <si>
+    <t>ORD027</t>
+  </si>
+  <si>
+    <t>ORD028</t>
+  </si>
+  <si>
+    <t>ORD029</t>
+  </si>
+  <si>
+    <t>ORD030</t>
+  </si>
+  <si>
+    <t>3月訂單資料</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -198,7 +307,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -211,13 +320,52 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -226,14 +374,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -241,6 +386,30 @@
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -522,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.1796875" customWidth="1"/>
@@ -530,44 +699,58 @@
     <col min="3" max="3" width="17.54296875" customWidth="1"/>
     <col min="4" max="4" width="10.54296875" customWidth="1"/>
     <col min="7" max="7" width="12.1796875" customWidth="1"/>
+    <col min="8" max="8" width="3.36328125" customWidth="1"/>
+    <col min="9" max="9" width="10.7265625" customWidth="1"/>
+    <col min="10" max="10" width="9.81640625" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="9.6328125" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" s="3">
+      <c r="G1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="7"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A2" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
         <v>46023</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -577,12 +760,12 @@
         <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="4">
+        <v>26</v>
+      </c>
+      <c r="E3" s="6">
         <v>599</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>2</v>
       </c>
       <c r="G3" s="4">
@@ -590,8 +773,8 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" s="3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
         <v>46024</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -601,12 +784,12 @@
         <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="4">
+        <v>27</v>
+      </c>
+      <c r="E4" s="6">
         <v>1890</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>1</v>
       </c>
       <c r="G4" s="4">
@@ -614,8 +797,8 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" s="3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
         <v>46025</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -625,12 +808,12 @@
         <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="4">
+        <v>28</v>
+      </c>
+      <c r="E5" s="6">
         <v>1290</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>2</v>
       </c>
       <c r="G5" s="4">
@@ -638,8 +821,8 @@
         <v>2580</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6" s="3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
         <v>46026</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -649,12 +832,12 @@
         <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="4">
+        <v>29</v>
+      </c>
+      <c r="E6" s="6">
         <v>890</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>3</v>
       </c>
       <c r="G6" s="4">
@@ -662,8 +845,8 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A7" s="3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
         <v>46027</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -673,12 +856,12 @@
         <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="4">
+        <v>30</v>
+      </c>
+      <c r="E7" s="6">
         <v>290</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="4">
@@ -686,8 +869,8 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A8" s="3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
         <v>46028</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -697,12 +880,12 @@
         <v>21</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="4">
+        <v>31</v>
+      </c>
+      <c r="E8" s="6">
         <v>1490</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>1</v>
       </c>
       <c r="G8" s="4">
@@ -710,8 +893,8 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A9" s="3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
         <v>46029</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -721,12 +904,12 @@
         <v>22</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="4">
+        <v>26</v>
+      </c>
+      <c r="E9" s="6">
         <v>450</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="4">
@@ -734,8 +917,8 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A10" s="3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
         <v>46030</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -745,12 +928,12 @@
         <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="4">
+        <v>32</v>
+      </c>
+      <c r="E10" s="6">
         <v>1690</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>2</v>
       </c>
       <c r="G10" s="4">
@@ -758,8 +941,8 @@
         <v>3380</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11" s="3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
         <v>46031</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -769,12 +952,12 @@
         <v>24</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="4">
+        <v>33</v>
+      </c>
+      <c r="E11" s="6">
         <v>790</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
       <c r="G11" s="4">
@@ -782,8 +965,8 @@
         <v>2370</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A12" s="3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
         <v>46032</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -793,12 +976,12 @@
         <v>25</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="4">
+        <v>34</v>
+      </c>
+      <c r="E12" s="6">
         <v>2490</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>1</v>
       </c>
       <c r="G12" s="4">
@@ -806,37 +989,594 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="3"/>
       <c r="F14">
         <v>24</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="3">
         <f>SUM(G3:G12)</f>
         <v>21318</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="4"/>
+        <v>36</v>
+      </c>
+      <c r="E15" s="3"/>
       <c r="F15">
         <v>2.4</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="3">
         <v>2131.8000000000002</v>
       </c>
     </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A17" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A18" s="2">
+        <v>46054</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="6">
+        <v>599</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" ref="G18:G27" si="1">E18*F18</f>
+        <v>1797</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A19" s="2">
+        <v>46055</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1290</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="4">
+        <f t="shared" si="1"/>
+        <v>1290</v>
+      </c>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A20" s="2">
+        <v>46056</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="6">
+        <v>890</v>
+      </c>
+      <c r="F20" s="1">
+        <v>4</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="1"/>
+        <v>3560</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A21" s="2">
+        <v>46057</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="6">
+        <v>450</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2</v>
+      </c>
+      <c r="G21" s="4">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A22" s="2">
+        <v>46058</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="6">
+        <v>790</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="1"/>
+        <v>1580</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A23" s="2">
+        <v>46059</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="6">
+        <v>2490</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="4">
+        <f t="shared" si="1"/>
+        <v>2490</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A24" s="2">
+        <v>46060</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="6">
+        <v>1890</v>
+      </c>
+      <c r="F24" s="1">
+        <v>2</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="1"/>
+        <v>3780</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A25" s="2">
+        <v>46061</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="6">
+        <v>290</v>
+      </c>
+      <c r="F25" s="1">
+        <v>6</v>
+      </c>
+      <c r="G25" s="4">
+        <f t="shared" si="1"/>
+        <v>1740</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A26" s="2">
+        <v>46062</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1690</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="1"/>
+        <v>1690</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A27" s="2">
+        <v>46063</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1490</v>
+      </c>
+      <c r="F27" s="1">
+        <v>3</v>
+      </c>
+      <c r="G27" s="4">
+        <f t="shared" si="1"/>
+        <v>4470</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" s="3">
+        <f>SUM(G18:G27)</f>
+        <v>23297</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G30" s="3">
+        <f>AVERAGE(G18:G27)</f>
+        <v>2329.6999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A32" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="6">
+        <v>1890</v>
+      </c>
+      <c r="F33" s="1">
+        <v>2</v>
+      </c>
+      <c r="G33" s="3">
+        <f>E33*F33</f>
+        <v>3780</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="2">
+        <v>46083</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="6">
+        <v>599</v>
+      </c>
+      <c r="F34" s="1">
+        <v>4</v>
+      </c>
+      <c r="G34" s="3">
+        <f t="shared" ref="G34:G42" si="2">E34*F34</f>
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="2">
+        <v>46084</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="6">
+        <v>1290</v>
+      </c>
+      <c r="F35" s="1">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3">
+        <f t="shared" si="2"/>
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="6">
+        <v>2490</v>
+      </c>
+      <c r="F36" s="1">
+        <v>2</v>
+      </c>
+      <c r="G36" s="3">
+        <f t="shared" si="2"/>
+        <v>4980</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="2">
+        <v>46086</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E37" s="6">
+        <v>790</v>
+      </c>
+      <c r="F37" s="1">
+        <v>5</v>
+      </c>
+      <c r="G37" s="3">
+        <f t="shared" si="2"/>
+        <v>3950</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="6">
+        <v>290</v>
+      </c>
+      <c r="F38" s="1">
+        <v>8</v>
+      </c>
+      <c r="G38" s="3">
+        <f t="shared" si="2"/>
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="2">
+        <v>46088</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="6">
+        <v>890</v>
+      </c>
+      <c r="F39" s="1">
+        <v>4</v>
+      </c>
+      <c r="G39" s="3">
+        <f t="shared" si="2"/>
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="2">
+        <v>46089</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="6">
+        <v>450</v>
+      </c>
+      <c r="F40" s="1">
+        <v>6</v>
+      </c>
+      <c r="G40" s="3">
+        <f t="shared" si="2"/>
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" s="6">
+        <v>1690</v>
+      </c>
+      <c r="F41" s="1">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3">
+        <f t="shared" si="2"/>
+        <v>5070</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" s="2">
+        <v>46091</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="6">
+        <v>1490</v>
+      </c>
+      <c r="F42" s="1">
+        <v>2</v>
+      </c>
+      <c r="G42" s="3">
+        <f t="shared" si="2"/>
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F43">
+        <f>SUM(F33:F42)</f>
+        <v>39</v>
+      </c>
+      <c r="G43" s="3">
+        <f>SUM(G33:G42)</f>
+        <v>35606</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44" s="3">
+        <v>3560</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A32:G32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
